--- a/logs/tasks-list/tasks-list-news-scape-FPA-AnPT-FPA-AnPT.xlsx
+++ b/logs/tasks-list/tasks-list-news-scape-FPA-AnPT-FPA-AnPT.xlsx
@@ -2363,9 +2363,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="caed7ae97c664de60029983d3ac4638e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e1819aac575aee29cb2a2f708b09de1" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
     <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
+    <xsd:import namespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2375,6 +2376,11 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2399,6 +2405,43 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8f7c344f-19d0-4f45-b23a-2df2b546d212" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4dc7bc77-2376-40bf-86a0-4a9e9b5c2537}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2502,7 +2545,12 @@
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
 </p:properties>
 </file>
 
@@ -2516,21 +2564,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2DCB1F6-65D9-41E2-8F81-B6B7E3279A7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9160F235-8519-47FB-960A-18F79E561E23}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
